--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$150</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5824" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5564" uniqueCount="876">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1386,6 +1386,13 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActCode"/&gt;
+  &lt;code value="PINSTRUCT"/&gt;
+  &lt;display value="Patient Medication Instructions"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -1393,150 +1400,6 @@
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ActCode</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>PINSTRUCT</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.coding.userSelected</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.additionalInstruction.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.additionalInstruction:instructionsPatient.text</t>
@@ -3193,11 +3056,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO157"/>
+  <dimension ref="A1:AO150"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="79.0546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="63.77734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="70.74609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.34765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.83203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -9239,7 +9102,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>81</v>
@@ -9278,7 +9141,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9299,21 +9162,21 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9333,19 +9196,23 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -9393,7 +9260,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9405,7 +9272,7 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -9414,32 +9281,34 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -9448,21 +9317,23 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -9486,31 +9357,31 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9522,7 +9393,7 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -9531,21 +9402,21 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9565,23 +9436,19 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>382</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>383</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -9590,7 +9457,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9496,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9641,7 +9508,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -9650,13 +9517,13 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>450</v>
+        <v>386</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -9664,18 +9531,18 @@
         <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -9684,19 +9551,19 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>157</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9734,31 +9601,31 @@
         <v>81</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>457</v>
+        <v>391</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -9767,21 +9634,21 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>386</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9792,7 +9659,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -9804,17 +9671,19 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9824,7 +9693,7 @@
         <v>81</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>81</v>
@@ -9863,13 +9732,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -9884,21 +9753,21 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>468</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9924,14 +9793,16 @@
         <v>382</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9941,7 +9812,7 @@
         <v>81</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>81</v>
@@ -9980,7 +9851,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -10001,21 +9872,21 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>476</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10038,20 +9909,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>219</v>
+        <v>382</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -10099,7 +9966,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -10120,21 +9987,21 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>485</v>
+        <v>420</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10148,7 +10015,7 @@
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
@@ -10157,19 +10024,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>382</v>
+        <v>461</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -10218,7 +10085,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -10239,25 +10106,23 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>81</v>
       </c>
@@ -10275,23 +10140,19 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>183</v>
+        <v>382</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -10315,13 +10176,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -10339,19 +10200,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -10360,32 +10221,32 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -10397,15 +10258,17 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -10442,31 +10305,31 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -10486,14 +10349,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>154</v>
+        <v>393</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10506,24 +10369,26 @@
         <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -10559,19 +10424,19 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10592,7 +10457,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>386</v>
+        <v>133</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -10603,10 +10468,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10629,19 +10494,17 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10690,7 +10553,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10711,21 +10574,21 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10739,7 +10602,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>81</v>
@@ -10748,19 +10611,17 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>382</v>
+        <v>478</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10770,7 +10631,7 @@
         <v>81</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>81</v>
@@ -10809,7 +10670,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10821,7 +10682,7 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>483</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -10830,21 +10691,21 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10864,16 +10725,16 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>382</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>383</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
+        <v>384</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10924,7 +10785,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10936,7 +10797,7 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -10945,57 +10806,55 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>508</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>509</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>510</v>
+        <v>389</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -11031,31 +10890,31 @@
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>391</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
@@ -11064,7 +10923,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>514</v>
+        <v>386</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -11075,10 +10934,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11098,16 +10957,16 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>382</v>
+        <v>488</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>384</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11146,19 +11005,17 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>385</v>
+        <v>492</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11170,7 +11027,7 @@
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -11179,7 +11036,7 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>386</v>
+        <v>493</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -11190,21 +11047,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="D69" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -11213,20 +11072,18 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>496</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>388</v>
+        <v>497</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -11263,31 +11120,31 @@
         <v>81</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -11296,7 +11153,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>386</v>
+        <v>493</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -11307,46 +11164,42 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>382</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -11394,19 +11247,19 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
@@ -11415,7 +11268,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>386</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -11426,14 +11279,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11449,21 +11302,21 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>267</v>
+        <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>388</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -11499,19 +11352,19 @@
         <v>81</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>391</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11523,7 +11376,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11532,7 +11385,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>523</v>
+        <v>386</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -11541,12 +11394,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11560,7 +11413,7 @@
         <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>81</v>
@@ -11569,18 +11422,18 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>525</v>
+        <v>267</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -11628,7 +11481,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11637,10 +11490,10 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>530</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -11649,21 +11502,21 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11683,23 +11536,27 @@
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>382</v>
+        <v>267</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>383</v>
+        <v>513</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q73" s="2"/>
+      <c r="Q73" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="R73" t="s" s="2">
         <v>81</v>
       </c>
@@ -11743,7 +11600,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>385</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11752,10 +11609,10 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
@@ -11764,32 +11621,32 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>386</v>
+        <v>518</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -11798,21 +11655,23 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>521</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>388</v>
+        <v>522</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>389</v>
+        <v>523</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11848,31 +11707,31 @@
         <v>81</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>391</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -11881,7 +11740,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>527</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11892,10 +11751,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11918,13 +11777,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11963,17 +11822,19 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11994,7 +11855,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -12005,14 +11866,12 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>81</v>
       </c>
@@ -12033,16 +11892,20 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -12090,7 +11953,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -12111,7 +11974,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -12122,10 +11985,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12145,19 +12008,23 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>382</v>
+        <v>533</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>383</v>
+        <v>541</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -12205,7 +12072,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>385</v>
+        <v>543</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -12217,7 +12084,7 @@
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>81</v>
@@ -12226,7 +12093,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>386</v>
+        <v>539</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -12237,21 +12104,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -12260,20 +12127,18 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>388</v>
+        <v>545</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12298,43 +12163,43 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>548</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>391</v>
+        <v>549</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>81</v>
@@ -12343,7 +12208,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>386</v>
+        <v>550</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -12352,12 +12217,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12371,7 +12236,7 @@
         <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>81</v>
@@ -12380,22 +12245,22 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>267</v>
+        <v>521</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N79" t="s" s="2">
         <v>553</v>
       </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="R79" t="s" s="2">
         <v>81</v>
       </c>
@@ -12439,7 +12304,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12448,7 +12313,7 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>555</v>
+        <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -12460,21 +12325,21 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>557</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12497,24 +12362,20 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>267</v>
+        <v>521</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q80" t="s" s="2">
-        <v>563</v>
-      </c>
+      <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
         <v>81</v>
       </c>
@@ -12558,7 +12419,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12567,7 +12428,7 @@
         <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>555</v>
+        <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>102</v>
@@ -12579,21 +12440,21 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>566</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12607,7 +12468,7 @@
         <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>81</v>
@@ -12616,20 +12477,16 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -12677,7 +12534,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12698,7 +12555,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>574</v>
+        <v>539</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -12709,10 +12566,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12735,13 +12592,13 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12792,7 +12649,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12813,7 +12670,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>574</v>
+        <v>539</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12822,12 +12679,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12841,7 +12698,7 @@
         <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>81</v>
@@ -12850,20 +12707,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12887,13 +12740,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>81</v>
+        <v>548</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -12911,7 +12764,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12932,7 +12785,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>586</v>
+        <v>550</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -12943,10 +12796,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12957,7 +12810,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -12969,20 +12822,18 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -13006,13 +12857,11 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>81</v>
+        <v>574</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -13030,13 +12879,13 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
@@ -13051,7 +12900,7 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>586</v>
+        <v>386</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -13062,10 +12911,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13076,7 +12925,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -13088,15 +12937,17 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>110</v>
+        <v>577</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -13121,13 +12972,13 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>594</v>
+        <v>81</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>595</v>
+        <v>81</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -13145,13 +12996,13 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
@@ -13166,7 +13017,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>597</v>
+        <v>386</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -13177,10 +13028,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13191,7 +13042,7 @@
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>91</v>
@@ -13203,22 +13054,24 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>568</v>
+        <v>110</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q86" t="s" s="2">
-        <v>601</v>
-      </c>
+      <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
         <v>81</v>
       </c>
@@ -13238,13 +13091,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>81</v>
+        <v>587</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -13262,13 +13115,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -13283,7 +13136,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -13292,12 +13145,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13311,7 +13164,7 @@
         <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>81</v>
@@ -13320,13 +13173,13 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13377,7 +13230,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13398,7 +13251,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13407,12 +13260,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13426,7 +13279,7 @@
         <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>81</v>
@@ -13435,15 +13288,17 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>580</v>
+        <v>183</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N88" s="2"/>
+      <c r="N88" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -13468,13 +13323,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>601</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>602</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13492,7 +13347,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13513,7 +13368,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13522,12 +13377,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13541,7 +13396,7 @@
         <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>81</v>
@@ -13550,15 +13405,17 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13583,13 +13440,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>81</v>
+        <v>611</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13607,7 +13464,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13628,21 +13485,21 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>614</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13665,16 +13522,20 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13700,11 +13561,9 @@
       <c r="X90" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y90" t="s" s="2">
-        <v>594</v>
-      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13722,7 +13581,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13743,21 +13602,21 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>81</v>
+        <v>623</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13768,10 +13627,10 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>81</v>
@@ -13780,18 +13639,18 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13819,7 +13678,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -13837,13 +13696,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -13858,21 +13717,21 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>386</v>
+        <v>630</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>81</v>
+        <v>631</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13883,7 +13742,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>81</v>
@@ -13895,18 +13754,20 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>624</v>
+        <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
@@ -13930,13 +13791,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>81</v>
+        <v>638</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13954,13 +13815,13 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>81</v>
@@ -13975,21 +13836,21 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>386</v>
+        <v>640</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>81</v>
+        <v>641</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14003,7 +13864,7 @@
         <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>81</v>
@@ -14012,20 +13873,16 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>110</v>
+        <v>478</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -14049,13 +13906,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>634</v>
+        <v>81</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>635</v>
+        <v>81</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -14073,7 +13930,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14094,21 +13951,21 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>81</v>
+        <v>646</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14122,22 +13979,22 @@
         <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>639</v>
+        <v>382</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>640</v>
+        <v>383</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>641</v>
+        <v>384</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14188,7 +14045,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>642</v>
+        <v>385</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14200,7 +14057,7 @@
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -14209,7 +14066,7 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>643</v>
+        <v>386</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
@@ -14220,21 +14077,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -14243,19 +14100,19 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>645</v>
+        <v>388</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>646</v>
+        <v>389</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>647</v>
+        <v>157</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14281,66 +14138,66 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="Z95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="AA95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>652</v>
-      </c>
       <c r="B96" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14354,7 +14211,7 @@
         <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>81</v>
@@ -14363,18 +14220,18 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>653</v>
+        <v>183</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -14401,10 +14258,10 @@
         <v>187</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -14422,7 +14279,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14443,21 +14300,21 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>660</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14471,7 +14328,7 @@
         <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>81</v>
@@ -14480,19 +14337,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>183</v>
+        <v>658</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -14517,29 +14374,29 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>667</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14560,23 +14417,25 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>669</v>
+        <v>640</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>657</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
       </c>
@@ -14597,17 +14456,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>183</v>
+        <v>667</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="O98" t="s" s="2">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14632,11 +14493,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>675</v>
+        <v>81</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -14654,7 +14517,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14675,21 +14538,21 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>677</v>
+        <v>640</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>678</v>
+        <v>664</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14709,23 +14572,19 @@
         <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>183</v>
+        <v>382</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>680</v>
+        <v>383</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14749,13 +14608,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>684</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14773,7 +14632,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>385</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14785,7 +14644,7 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
@@ -14794,25 +14653,25 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>687</v>
+        <v>386</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>688</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14828,18 +14687,20 @@
         <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>525</v>
+        <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>388</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14876,19 +14737,19 @@
         <v>81</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>391</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14900,7 +14761,7 @@
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>81</v>
@@ -14909,21 +14770,21 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>693</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14931,30 +14792,32 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>382</v>
+        <v>675</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>383</v>
+        <v>676</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -15003,7 +14866,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>385</v>
+        <v>679</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -15015,7 +14878,7 @@
         <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>81</v>
@@ -15024,53 +14887,53 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>386</v>
+        <v>509</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>81</v>
+        <v>680</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>135</v>
+        <v>675</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>388</v>
+        <v>683</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>389</v>
+        <v>684</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>157</v>
+        <v>685</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15108,31 +14971,31 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>391</v>
+        <v>686</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>81</v>
@@ -15141,21 +15004,21 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>386</v>
+        <v>518</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>81</v>
+        <v>687</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15178,17 +15041,19 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>183</v>
+        <v>689</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -15213,31 +15078,29 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>700</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>701</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15258,23 +15121,25 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>81</v>
+        <v>695</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="D104" t="s" s="2">
         <v>81</v>
       </c>
@@ -15286,7 +15151,7 @@
         <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>81</v>
@@ -15295,19 +15160,19 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>705</v>
+        <v>667</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15344,17 +15209,19 @@
         <v>81</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15375,25 +15242,23 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>711</v>
+        <v>696</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>81</v>
       </c>
@@ -15405,29 +15270,25 @@
         <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>714</v>
+        <v>382</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>715</v>
+        <v>383</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -15475,7 +15336,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>710</v>
+        <v>385</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15487,7 +15348,7 @@
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>81</v>
@@ -15496,32 +15357,32 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>687</v>
+        <v>386</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>711</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -15533,15 +15394,17 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15578,31 +15441,31 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>81</v>
@@ -15620,44 +15483,44 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>135</v>
+        <v>675</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>388</v>
+        <v>676</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>389</v>
+        <v>677</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>157</v>
+        <v>678</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15695,31 +15558,31 @@
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>391</v>
+        <v>679</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>81</v>
@@ -15728,21 +15591,21 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>386</v>
+        <v>509</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>81</v>
+        <v>680</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15765,16 +15628,16 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>722</v>
+        <v>675</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>724</v>
+        <v>684</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>725</v>
+        <v>685</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15824,7 +15687,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>726</v>
+        <v>686</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15845,21 +15708,21 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>556</v>
+        <v>518</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>727</v>
+        <v>687</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15867,7 +15730,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>90</v>
@@ -15882,18 +15745,20 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15941,7 +15806,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15962,21 +15827,21 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>565</v>
+        <v>715</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>734</v>
+        <v>716</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15996,23 +15861,19 @@
         <v>81</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>736</v>
+        <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>737</v>
+        <v>383</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>740</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>81</v>
       </c>
@@ -16048,17 +15909,19 @@
         <v>81</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AC110" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>741</v>
+        <v>385</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16070,7 +15933,7 @@
         <v>81</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>81</v>
@@ -16079,59 +15942,55 @@
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>742</v>
+        <v>386</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>743</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>744</v>
+        <v>718</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>745</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>714</v>
+        <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>746</v>
+        <v>388</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>738</v>
+        <v>389</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>740</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -16167,31 +16026,31 @@
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>741</v>
+        <v>391</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>81</v>
@@ -16200,21 +16059,21 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>742</v>
+        <v>386</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>743</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>747</v>
+        <v>719</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>748</v>
+        <v>719</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16222,28 +16081,28 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>382</v>
+        <v>720</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>383</v>
+        <v>721</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>384</v>
+        <v>722</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16294,7 +16153,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>385</v>
+        <v>723</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16306,7 +16165,7 @@
         <v>81</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>81</v>
@@ -16315,7 +16174,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>386</v>
+        <v>724</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -16324,45 +16183,43 @@
         <v>81</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>135</v>
+        <v>720</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>388</v>
+        <v>726</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>727</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -16399,31 +16256,31 @@
         <v>81</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>391</v>
+        <v>728</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>81</v>
@@ -16432,7 +16289,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>386</v>
+        <v>729</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -16441,12 +16298,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>752</v>
+        <v>730</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16454,13 +16311,13 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>81</v>
@@ -16469,18 +16326,20 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>722</v>
+        <v>675</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
       </c>
@@ -16528,7 +16387,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16549,21 +16408,21 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>556</v>
+        <v>736</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>727</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16571,13 +16430,13 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>81</v>
@@ -16586,18 +16445,18 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>722</v>
+        <v>675</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16645,7 +16504,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16666,21 +16525,21 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>565</v>
+        <v>736</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>734</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16700,23 +16559,19 @@
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>760</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16764,7 +16619,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16782,24 +16637,24 @@
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>81</v>
+        <v>746</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>763</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16911,14 +16766,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16940,14 +16795,12 @@
         <v>135</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>388</v>
+        <v>136</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16986,9 +16839,7 @@
       <c r="AB118" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC118" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="AC118" s="2"/>
       <c r="AD118" t="s" s="2">
         <v>81</v>
       </c>
@@ -17017,7 +16868,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -17026,43 +16877,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -17111,19 +16966,19 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>770</v>
+        <v>391</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>81</v>
@@ -17132,7 +16987,7 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>771</v>
+        <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -17141,12 +16996,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17154,28 +17009,28 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>767</v>
+        <v>382</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>773</v>
+        <v>383</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>774</v>
+        <v>384</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17226,7 +17081,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>775</v>
+        <v>385</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17238,7 +17093,7 @@
         <v>81</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>81</v>
@@ -17247,7 +17102,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>776</v>
+        <v>386</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -17258,10 +17113,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17272,7 +17127,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>81</v>
@@ -17281,23 +17136,19 @@
         <v>81</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>722</v>
+        <v>135</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>778</v>
+        <v>136</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>781</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
@@ -17333,31 +17184,31 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>782</v>
+        <v>391</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>81</v>
@@ -17366,7 +17217,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>783</v>
+        <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -17377,10 +17228,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>784</v>
+        <v>761</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17388,7 +17239,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>90</v>
@@ -17400,27 +17251,27 @@
         <v>81</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>722</v>
+        <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" t="s" s="2">
-        <v>787</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>81</v>
+        <v>765</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>81</v>
@@ -17462,10 +17313,10 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>788</v>
+        <v>766</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>90</v>
@@ -17474,7 +17325,7 @@
         <v>81</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>81</v>
@@ -17483,7 +17334,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>783</v>
+        <v>133</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -17492,12 +17343,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17505,13 +17356,13 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>81</v>
@@ -17520,13 +17371,13 @@
         <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>790</v>
+        <v>368</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17577,7 +17428,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17595,10 +17446,10 @@
         <v>81</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>793</v>
+        <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>794</v>
+        <v>133</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17609,42 +17460,46 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>795</v>
+        <v>772</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>795</v>
+        <v>772</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
       </c>
@@ -17692,19 +17547,19 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>81</v>
@@ -17713,7 +17568,7 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>386</v>
+        <v>133</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
@@ -17724,10 +17579,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>796</v>
+        <v>773</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>796</v>
+        <v>773</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17738,7 +17593,7 @@
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>81</v>
@@ -17750,15 +17605,17 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>135</v>
+        <v>743</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>136</v>
+        <v>774</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>775</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>776</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17795,29 +17652,31 @@
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC125" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>391</v>
+        <v>773</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>81</v>
@@ -17826,7 +17685,7 @@
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>81</v>
+        <v>777</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
@@ -17837,14 +17696,12 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>798</v>
-      </c>
+        <v>778</v>
+      </c>
+      <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17865,17 +17722,15 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>799</v>
+        <v>382</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>800</v>
+        <v>383</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>802</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17924,19 +17779,19 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
@@ -17945,7 +17800,7 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
@@ -17956,21 +17811,21 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>803</v>
+        <v>779</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>804</v>
+        <v>779</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>81</v>
@@ -17982,15 +17837,17 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -18039,19 +17896,19 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -18071,42 +17928,46 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>806</v>
+        <v>780</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>136</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -18142,19 +18003,19 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18175,7 +18036,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -18186,10 +18047,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>807</v>
+        <v>781</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>808</v>
+        <v>781</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18197,7 +18058,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>90</v>
@@ -18212,24 +18073,22 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>104</v>
+        <v>675</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>809</v>
+        <v>782</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>811</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>812</v>
+        <v>81</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>81</v>
@@ -18271,10 +18130,10 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>90</v>
@@ -18283,7 +18142,7 @@
         <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>81</v>
@@ -18292,7 +18151,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>133</v>
+        <v>784</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -18303,10 +18162,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>815</v>
+        <v>785</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18314,7 +18173,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>90</v>
@@ -18329,13 +18188,13 @@
         <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>368</v>
+        <v>786</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>816</v>
+        <v>787</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>817</v>
+        <v>788</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18386,7 +18245,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18407,7 +18266,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>133</v>
+        <v>789</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -18418,46 +18277,42 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>819</v>
+        <v>790</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>819</v>
+        <v>790</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>135</v>
+        <v>786</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>394</v>
+        <v>791</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>792</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>81</v>
       </c>
@@ -18505,19 +18360,19 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>396</v>
+        <v>790</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>81</v>
@@ -18526,7 +18381,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>133</v>
+        <v>789</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18535,12 +18390,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18554,7 +18409,7 @@
         <v>90</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>81</v>
@@ -18563,18 +18418,20 @@
         <v>81</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>790</v>
+        <v>496</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>821</v>
+        <v>794</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>822</v>
+        <v>795</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>797</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18622,7 +18479,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18640,10 +18497,10 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>798</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
@@ -18652,12 +18509,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18671,7 +18528,7 @@
         <v>90</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>81</v>
@@ -18680,15 +18537,17 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>382</v>
+        <v>592</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>383</v>
+        <v>801</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18737,7 +18596,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>385</v>
+        <v>800</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18749,44 +18608,44 @@
         <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>81</v>
+        <v>804</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>386</v>
+        <v>805</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>81</v>
+        <v>806</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>81</v>
@@ -18795,17 +18654,15 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>135</v>
+        <v>675</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>388</v>
+        <v>808</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18854,78 +18711,76 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>391</v>
+        <v>807</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>81</v>
+        <v>810</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>386</v>
+        <v>811</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>81</v>
+        <v>812</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>135</v>
+        <v>786</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>394</v>
+        <v>814</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>395</v>
+        <v>815</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18973,28 +18828,28 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>396</v>
+        <v>813</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>81</v>
+        <v>817</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>133</v>
+        <v>818</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19005,10 +18860,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19031,13 +18886,13 @@
         <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>722</v>
+        <v>820</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19088,7 +18943,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19109,21 +18964,21 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19131,13 +18986,13 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>81</v>
@@ -19146,13 +19001,13 @@
         <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>833</v>
+        <v>743</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19203,7 +19058,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19221,10 +19076,10 @@
         <v>81</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>81</v>
+        <v>827</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -19235,10 +19090,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19261,13 +19116,13 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>833</v>
+        <v>382</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>838</v>
+        <v>383</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>839</v>
+        <v>384</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19318,7 +19173,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>837</v>
+        <v>385</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19330,7 +19185,7 @@
         <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>81</v>
@@ -19339,7 +19194,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>836</v>
+        <v>386</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19348,26 +19203,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>81</v>
@@ -19376,20 +19231,18 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>543</v>
+        <v>135</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>841</v>
+        <v>388</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>842</v>
+        <v>389</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>844</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>81</v>
       </c>
@@ -19437,28 +19290,28 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>840</v>
+        <v>391</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>845</v>
+        <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>846</v>
+        <v>386</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -19467,46 +19320,48 @@
         <v>81</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I140" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I140" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J140" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>639</v>
+        <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>848</v>
+        <v>394</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>849</v>
+        <v>395</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19554,42 +19409,42 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>847</v>
+        <v>396</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>851</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>852</v>
+        <v>133</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>853</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19597,7 +19452,7 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>90</v>
@@ -19612,15 +19467,17 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>722</v>
+        <v>606</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>855</v>
+        <v>833</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>834</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>835</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19645,34 +19502,32 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>81</v>
+        <v>836</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>837</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>90</v>
@@ -19687,26 +19542,28 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>857</v>
+        <v>827</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>859</v>
+        <v>839</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>841</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19727,16 +19584,16 @@
         <v>81</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="L142" t="s" s="2">
-        <v>861</v>
-      </c>
       <c r="M142" t="s" s="2">
-        <v>862</v>
+        <v>834</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>863</v>
+        <v>835</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19762,13 +19619,11 @@
         <v>81</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>81</v>
+        <v>842</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
@@ -19786,10 +19641,10 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>860</v>
+        <v>832</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>90</v>
@@ -19804,24 +19659,24 @@
         <v>81</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>864</v>
+        <v>827</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>865</v>
+        <v>838</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>81</v>
+        <v>839</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19835,7 +19690,7 @@
         <v>90</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>81</v>
@@ -19844,13 +19699,13 @@
         <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>867</v>
+        <v>183</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19877,13 +19732,13 @@
         <v>81</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>81</v>
+        <v>846</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>81</v>
+        <v>847</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>81</v>
@@ -19901,7 +19756,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19919,24 +19774,24 @@
         <v>81</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>81</v>
+        <v>848</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>81</v>
+        <v>850</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19944,13 +19799,13 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>81</v>
@@ -19959,13 +19814,13 @@
         <v>81</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>790</v>
+        <v>382</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>872</v>
+        <v>383</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>873</v>
+        <v>384</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20016,7 +19871,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>871</v>
+        <v>385</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20028,16 +19883,16 @@
         <v>81</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>874</v>
+        <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>875</v>
+        <v>386</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -20048,21 +19903,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>81</v>
@@ -20074,15 +19929,17 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>81</v>
@@ -20119,31 +19976,31 @@
         <v>81</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>81</v>
@@ -20163,14 +20020,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>877</v>
+        <v>853</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>877</v>
+        <v>853</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20186,21 +20043,23 @@
         <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>135</v>
+        <v>430</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>389</v>
+        <v>432</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>81</v>
       </c>
@@ -20248,7 +20107,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>391</v>
+        <v>436</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20260,7 +20119,7 @@
         <v>81</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>81</v>
@@ -20269,56 +20128,56 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J147" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>135</v>
+        <v>382</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>394</v>
+        <v>855</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>157</v>
+        <v>443</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>158</v>
+        <v>444</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
@@ -20367,19 +20226,19 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>81</v>
@@ -20388,21 +20247,21 @@
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>133</v>
+        <v>446</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>879</v>
+        <v>856</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>879</v>
+        <v>856</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20410,13 +20269,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>81</v>
@@ -20425,17 +20284,15 @@
         <v>81</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>653</v>
+        <v>857</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>880</v>
+        <v>858</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>882</v>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20460,32 +20317,34 @@
         <v>81</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>883</v>
+        <v>81</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>884</v>
+        <v>81</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AC148" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>879</v>
+        <v>856</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>90</v>
@@ -20497,40 +20356,38 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>81</v>
+        <v>860</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>886</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>887</v>
+        <v>862</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>888</v>
-      </c>
+        <v>862</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>81</v>
+        <v>863</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>81</v>
@@ -20542,16 +20399,16 @@
         <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>183</v>
+        <v>864</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20577,11 +20434,13 @@
         <v>81</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>889</v>
+        <v>81</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20599,13 +20458,13 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>81</v>
@@ -20617,24 +20476,24 @@
         <v>81</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>874</v>
+        <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>885</v>
+        <v>868</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>886</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20645,10 +20504,10 @@
         <v>79</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>81</v>
@@ -20657,15 +20516,17 @@
         <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>183</v>
+        <v>870</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20690,13 +20551,13 @@
         <v>81</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>893</v>
+        <v>81</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>894</v>
+        <v>81</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>81</v>
@@ -20714,13 +20575,13 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>81</v>
@@ -20729,842 +20590,23 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>81</v>
+        <v>874</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>895</v>
+        <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O152" s="2"/>
-      <c r="P152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>911</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>918</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>919</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>922</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO157" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO157">
+  <autoFilter ref="A1:AO150">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21574,7 +20616,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI156">
+  <conditionalFormatting sqref="A2:AI149">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
